--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:16:43+00:00</t>
+    <t>2026-09-02T13:31:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T13:31:10+00:00</t>
+    <t>2026-09-02T15:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:15:11+00:00</t>
+    <t>2026-09-02T15:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
